--- a/output/laminas_comunales/comunal_o_ocup_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C386"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,301 +375,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C2">
-        <v>49.6163099386096</v>
+        <v>69.98332932703011</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C3">
-        <v>49.548888248985</v>
+        <v>69.13824027908051</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C4">
-        <v>49.2345118215145</v>
+        <v>68.4793586801726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C5">
-        <v>48.2817471296168</v>
+        <v>68.3671586061006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C6">
-        <v>48.2612508503192</v>
+        <v>66.97359127898051</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C7">
-        <v>46.0427255554906</v>
+        <v>64.7771674092017</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="C8">
-        <v>44.8007948579559</v>
+        <v>64.0370852309694</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C9">
-        <v>44.2212492746757</v>
+        <v>63.3261736975899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C10">
-        <v>44.0486328686278</v>
+        <v>63.2130893455327</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C11">
-        <v>43.9086612883627</v>
+        <v>63.1449530335298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C12">
-        <v>43.4703938682116</v>
+        <v>62.437095199302</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C13">
-        <v>43.4152654102187</v>
+        <v>62.2896030523149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C14">
-        <v>43.049270690307</v>
+        <v>62.2628911680039</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C15">
-        <v>42.8936978333877</v>
+        <v>61.9595475656748</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C16">
-        <v>42.4724294835359</v>
+        <v>61.8116558465786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C17">
-        <v>42.2974772045979</v>
+        <v>61.7324013979031</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C18">
-        <v>42.2704089400445</v>
+        <v>61.6191451990632</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C19">
-        <v>41.8934679805745</v>
+        <v>61.3202872580163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C20">
-        <v>41.674228494083</v>
+        <v>61.2592295218753</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C21">
-        <v>41.4745038523549</v>
+        <v>61.076441541273</v>
       </c>
     </row>
     <row r="22">
@@ -684,472 +684,5467 @@
         </is>
       </c>
       <c r="C22">
-        <v>41.4314683880356</v>
+        <v>61.051430444705</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C23">
-        <v>41.3241713993549</v>
+        <v>60.8507252666325</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C24">
-        <v>41.1433013620637</v>
+        <v>60.7785957669063</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C25">
-        <v>41.0284497089955</v>
+        <v>60.6545948712518</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C26">
-        <v>40.6059554661795</v>
+        <v>60.5506043678087</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C27">
-        <v>40.259045573372</v>
+        <v>60.5190990684319</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C28">
-        <v>40.1568225776779</v>
+        <v>60.5145859133888</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C29">
-        <v>40.0686886368826</v>
+        <v>59.8199192336589</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C30">
-        <v>39.5409843827148</v>
+        <v>59.3155217019148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C31">
-        <v>39.2581227207461</v>
+        <v>59.2381008069232</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C32">
-        <v>39.0118735096198</v>
+        <v>59.230992589073</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C33">
-        <v>38.6896034655115</v>
+        <v>58.6520062077175</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C34">
-        <v>38.190198752501</v>
+        <v>58.6426620357808</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C35">
-        <v>38.0798897390573</v>
+        <v>58.1224518487277</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C36">
-        <v>37.6536812371721</v>
+        <v>58.0611285064492</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="C37">
-        <v>37.5024077819513</v>
+        <v>57.7807854044568</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C38">
-        <v>37.3842352914107</v>
+        <v>57.6736755913903</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C39">
-        <v>37.2534900024384</v>
+        <v>57.6244912846502</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C40">
-        <v>37.1171769278512</v>
+        <v>57.284979539738</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C41">
-        <v>37.0288863776046</v>
+        <v>57.0104982921439</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C42">
-        <v>36.2406088449008</v>
+        <v>56.8806435867936</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="C43">
-        <v>36.0693065055124</v>
+        <v>56.8231481481481</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C44">
-        <v>35.7951185114417</v>
+        <v>56.7515593969399</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="C45">
-        <v>35.544726872785</v>
+        <v>56.7055714600308</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C46">
-        <v>35.3926758412076</v>
+        <v>56.2611576670237</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C47">
-        <v>35.212516999289</v>
+        <v>56.1499230994235</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C48">
-        <v>35.0108778540349</v>
+        <v>56.0416181210921</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C49">
-        <v>34.5490207199032</v>
+        <v>55.968130839639</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C50">
-        <v>34.1622632445786</v>
+        <v>55.7444290497633</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C51">
-        <v>33.9662069862746</v>
+        <v>55.6643356643357</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C52">
-        <v>33.9059987631416</v>
+        <v>55.6421915973888</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tiltil</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>55.6064185863359</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>55.5779488218216</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>55.5532913704358</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>55.3953136665582</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>55.1121385407795</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>55.0789591745177</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>54.9694625407166</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>54.7484905925302</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>54.4972893050764</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>54.4942916867664</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>54.3692543817794</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>53.9908749329039</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>53.9473152568502</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>53.8767921146953</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>53.4548480923489</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>53.3471200980392</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>53.3233276157804</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>53.1582525103304</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>52.8980907123251</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>52.6670728707184</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>52.6498720943165</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>52.5807569065558</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>52.4895144664818</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>52.4611979604415</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>52.4306003642047</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>52.2667014922431</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>52.0486620617253</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>52.0486383015749</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>52.0118304274083</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>51.7899545736114</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>51.6577648913983</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>51.5772645812968</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>51.4902907043548</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>51.4176022979934</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>51.3166832535583</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>51.3142314044436</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>51.259542435076</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>51.1903493348962</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>51.1663286004057</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>50.7531204992799</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>50.7118188024577</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>50.6809787626962</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>50.3811990347812</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>50.3582788320646</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>49.9372087471848</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>49.6642029523338</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tiltil</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>49.6163099386096</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>49.548888248985</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>49.3895792456944</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>49.2944966199356</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>49.2345118215145</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>49.1895475151826</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>49.1071874843805</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>48.2817471296168</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>48.2678051153519</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>48.2612508503192</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>48.2562396620205</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>48.0492150946696</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>48.0243121589304</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>47.8900639124992</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>47.8715365239295</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>47.6068514908671</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>47.5749966413219</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>47.5197740112994</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>47.4998183007486</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>47.4588520539003</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>47.4385824368658</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>47.3529893083133</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>47.0729415784079</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>46.9158367998655</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>46.8904063013543</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>46.868797756995</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>46.8374755197194</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>46.8371528862588</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>46.8240552056317</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>46.6878986352102</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>46.6839346018808</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>46.5483863871351</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>46.3570340542964</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>46.2933706284047</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>46.1376165257518</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>46.1210064747712</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>46.0427255554906</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>45.8951728297625</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>45.8817150015893</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>45.8276679777918</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>45.7704167233483</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>45.7512163895562</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>45.5858898583357</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>13505</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>San Pedro</t>
         </is>
       </c>
-      <c r="C53">
+      <c r="C142">
+        <v>45.3526970954357</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>45.3379593212721</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>45.2147592966273</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>44.8007948579559</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>44.7484302372992</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>44.6877305918089</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>44.4613206947007</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>44.2212492746757</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>44.1854990583804</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>44.082189112864</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>44.0486328686278</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>44.0162218733647</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>43.9086612883627</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>43.7889747214994</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>43.7185389809699</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>43.6270608880183</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>43.5337447613207</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>43.5223644245996</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>43.4703938682116</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>43.4228894432112</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>43.4194861553823</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>43.4152654102187</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>43.3789581974206</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>43.2486995006546</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>43.2018303597205</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>43.049270690307</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>42.9461727135849</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>42.8936978333877</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>42.7781650301047</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>42.6835270849554</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>42.5211054557348</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Tiltil</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>42.5152413906739</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>42.4724294835359</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>42.2974772045979</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>42.2704089400445</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>42.1146625562198</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>41.8934679805745</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>41.7551723017961</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>41.7137090477529</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>41.674228494083</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>41.6140128175871</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>41.4745038523549</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>41.4509407546972</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>41.4314683880356</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>41.3241713993549</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>41.2829318009547</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>41.1433013620637</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>41.0284497089955</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>40.626532559363</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>40.6059554661795</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>40.5743593409343</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Tiltil</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>40.4053409632809</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>40.3900889993415</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>40.259045573372</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>40.1568225776779</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>40.0686886368826</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>40.0306524874935</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>39.9557760080553</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>39.8806720050243</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>39.6883428457912</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>39.6021560063025</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>39.6003275558632</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>39.5409843827148</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>39.5355121765117</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>39.5301466594242</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>39.386679264525</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>39.2581227207461</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>39.2505496606443</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>39.0983440507254</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>39.0118735096198</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>38.9967721933439</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>38.7245554561577</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>38.6896034655115</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>38.4901604994276</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>38.2632685854719</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>38.190198752501</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>38.1747162101444</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>38.0798897390573</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>37.9114362623597</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>37.7267335144797</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>37.6536812371721</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>37.6444351674736</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>37.61177890994</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>37.577413091847</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>37.5024077819513</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>37.4031266454565</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>37.3842352914107</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>37.2534900024384</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>37.1171769278512</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>37.0288863776046</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>36.7319402715923</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>36.4550934684324</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>36.3981361887699</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>36.3869291162225</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>36.3299289830201</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>36.2406088449008</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>36.0693764741332</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>36.0693065055124</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>36.0345031559462</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>35.9495757231633</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>35.9084873568259</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>35.9008993102149</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>35.7951185114417</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>35.5597271002382</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>35.544726872785</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>35.3926758412076</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>35.2556180148573</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>35.212516999289</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>35.0327208658445</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>35.0108778540349</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>34.9830666092967</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>34.8446539309943</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>34.7983985260771</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>34.7052911659653</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>34.68549063461</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>34.6488618818963</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>34.5508390918065</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>34.5490207199032</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>34.5119326119022</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>34.4482312224248</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>34.4273119645141</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>34.1908075740411</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>34.1622632445786</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>34.0603657193214</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>34.0362565547468</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>34.0062414667447</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>33.9906251408482</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>33.9662069862746</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>33.9059987631416</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>33.8995593037036</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>33.8995264566605</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>33.8363945714936</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>33.7958788364559</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>33.7471621215022</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>33.4039616271728</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>33.3019212244141</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>33.1327575628864</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>33.1021697155274</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>33.0586445918316</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>33.0043221783371</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>33.0027606631544</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>32.8293543274884</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>32.7909414460533</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>32.7472689819344</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>32.6764197384224</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>32.5533661740558</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>32.48838007903</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>32.4820810882725</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>31.7643241840244</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>31.6718131912489</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>31.6013755126755</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>31.4024128456122</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>31.3743876693517</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>31.29408377717</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>31.2893411665967</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>30.9698750030222</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>30.8684700702735</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>30.6518027518329</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>30.4575391098061</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>30.3649964231284</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>30.2557896735004</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>30.2420956466476</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>30.2131355002002</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>30.1439003436426</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>29.9899162510007</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>29.8896192484187</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>29.8824574450504</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>29.7940337451685</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>29.7543199150497</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>29.7175620293542</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>29.6781481924826</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>29.5953763175231</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>29.4079878115138</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>29.3997965412004</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>29.3281194454319</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>29.3258771811051</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>29.2233205116737</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>29.2079726722589</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>29.1909116098642</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>28.3735194585448</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>28.36115975404</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>28.356890459364</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>28.1725888324873</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C325">
         <v>27.6264767703124</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>26.241302972802</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>26.138532860649</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>25.4626252310087</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>24.7469779439089</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>24.7185750335147</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>23.6875752105896</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>21.7835561897715</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>17.9657179818887</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Tiltil</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>17.844426184607</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>17.651930969688</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>17.46094257909</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>16.0627243408415</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>15.8196288224027</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>15.6974709022491</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>15.6287410812623</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>15.413735627313</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>15.2989733629301</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>15.1774451794741</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>15.1685194363804</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>15.1018607635547</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>15.0614472060169</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>14.8607378451014</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>14.8299516908213</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>14.6735447217776</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>14.3359796138391</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>14.0671443426911</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>14.0404497773753</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>13.9585236979063</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>13.8823733819825</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>13.8733680517884</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>13.8511682116333</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>13.8323433224321</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>13.6643266908213</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>13.6642532434365</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>13.5385496476056</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>13.4312300899793</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>13.2316778641374</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>13.026150814974</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>12.9051828739816</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>12.8989215865472</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>12.7859911602732</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>12.7179677317873</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>12.6925334991021</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>12.6232601749969</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>12.6112759643917</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>12.4764194743375</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>12.3020118016495</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>12.2077548921755</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>12.1068963920152</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>11.7264017033357</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>11.6363063850586</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>11.5688849970811</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>11.5477984262515</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>11.5134036988605</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>11.4716945646041</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>11.4226299949841</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>11.3625648279114</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>11.3124488124488</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>11.2985419536466</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>11.1558235426048</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>7.47953440777693</v>
       </c>
     </row>
   </sheetData>
